--- a/outputs/gate_report_2026-05-26_daily_quality.xlsx
+++ b/outputs/gate_report_2026-05-26_daily_quality.xlsx
@@ -11,7 +11,7 @@
     <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'quality'!$A$1:$F$568</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'quality'!$A$1:$F$569</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'summary'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F568"/>
+  <dimension ref="A1:F569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>S7 1003</t>
+          <t>U6 627</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>U6 105</t>
+          <t>S7 1003</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>S7 3031</t>
+          <t>U6 105</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>S7 2629</t>
+          <t>S7 3031</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>22:39</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>U6 427</t>
+          <t>S7 2629</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>22:39</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>U6 93</t>
+          <t>U6 427</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>S7 3041</t>
+          <t>U6 93</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>U6 261</t>
+          <t>S7 3041</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>U6 279</t>
+          <t>U6 261</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1960,29 +1960,29 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>S7 2169</t>
+          <t>U6 279</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Mineralnye Vody</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2002,19 +2002,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Mineralnye Vody</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2024,29 +2024,29 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>S7 2509</t>
+          <t>S7 2169</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Novosibirsk</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2066,19 +2066,19 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2088,29 +2088,29 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S7 2507</t>
+          <t>S7 2509</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Novosibirsk</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2130,19 +2130,19 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2152,29 +2152,29 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>S7 1073</t>
+          <t>S7 2507</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2194,19 +2194,19 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Samara</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2216,29 +2216,29 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S7 1137</t>
+          <t>S7 1073</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2258,19 +2258,19 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Ufa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2280,29 +2280,29 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>U6 167</t>
+          <t>S7 1137</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Kaliningrad</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2322,19 +2322,19 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Kaliningrad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2344,29 +2344,29 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>U6 299</t>
+          <t>U6 167</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Yekaterinburg</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Yekaterinburg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2408,29 +2408,29 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>S7 1007</t>
+          <t>U6 299</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2450,19 +2450,19 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2472,29 +2472,29 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>S7 2505</t>
+          <t>S7 1007</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Novosibirsk</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2536,29 +2536,29 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>S7 1213</t>
+          <t>S7 2505</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Kaliningrad</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Kaliningrad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2600,29 +2600,29 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>S7 1055</t>
+          <t>S7 1213</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Kazan</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Kazan</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>S7 2145</t>
+          <t>S7 1055</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Volgograd</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>S7 3045</t>
+          <t>S7 2145</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2711,14 +2711,14 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Chita</t>
+          <t>Volgograd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2738,19 +2738,19 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Chita</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>U6 9265</t>
+          <t>S7 3045</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Novosibirsk</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2834,19 +2834,19 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2856,22 +2856,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>U6 1387</t>
+          <t>U6 9265</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Vladikavkaz</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Vladikavkaz</t>
         </is>
       </c>
     </row>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>U6 2969</t>
+          <t>U6 1387</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ET 761</t>
+          <t>U6 2969</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EK 132</t>
+          <t>ET 761</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>S7 3745</t>
+          <t>EK 132</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>S7 3747</t>
+          <t>S7 3745</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>U6 2411</t>
+          <t>S7 3747</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>S7 3749</t>
+          <t>U6 2411</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>S7 4103</t>
+          <t>S7 3749</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>00:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>QNT 706</t>
+          <t>S7 4103</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>00:34</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>B2 958</t>
+          <t>QNT 706</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>B2 956</t>
+          <t>B2 958</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>FIE 314</t>
+          <t>B2 956</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>U6 2709</t>
+          <t>FIE 314</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>SMR 202</t>
+          <t>U6 2709</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>00:43</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>FIE 312</t>
+          <t>SMR 202</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>00:43</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>QNT 708</t>
+          <t>FIE 312</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>FIE 316</t>
+          <t>QNT 708</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>U6 783</t>
+          <t>FIE 316</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>U6 2633</t>
+          <t>U6 783</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>MS 728</t>
+          <t>U6 2633</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>01:11</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>S7 4261</t>
+          <t>MS 728</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:11</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>U6 8253</t>
+          <t>S7 4261</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -3656,22 +3656,22 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>S7 4263</t>
+          <t>U6 8253</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>multiple numeric gates</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>11, 7</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -3698,19 +3698,19 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>multiple numeric gates</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Tashkent</t>
+          <t>11, 7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -3730,19 +3730,19 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Tashkent</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3752,29 +3752,29 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EK 134</t>
+          <t>S7 4263</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -3794,19 +3794,19 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Dubai</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3816,29 +3816,29 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>S7 3235</t>
+          <t>EK 134</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Ashgabat</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -3858,19 +3858,19 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Ashgabat</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -3880,29 +3880,29 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>MS 730</t>
+          <t>S7 3235</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -3922,19 +3922,19 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Cairo</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -3944,22 +3944,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>U6 2803</t>
+          <t>MS 730</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -4018,19 +4018,19 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Bishkek</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Z7 966</t>
+          <t>U6 2803</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Osh</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -4114,19 +4114,19 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Osh</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4136,22 +4136,22 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Z7 884</t>
+          <t>Z7 966</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -4210,19 +4210,19 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Bishkek</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -4232,22 +4232,22 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Z7 960</t>
+          <t>Z7 884</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Bishkek</t>
         </is>
       </c>
     </row>
@@ -4323,17 +4323,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SVO</t>
+          <t>DME</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>SU 6807</t>
+          <t>Z7 960</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>SU 6699</t>
+          <t>SU 6807</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>SU 6127</t>
+          <t>SU 6699</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>SU 6167</t>
+          <t>SU 6127</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>SU 1138</t>
+          <t>SU 6167</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>SU 6855</t>
+          <t>SU 1138</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>SU 6481</t>
+          <t>SU 6855</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>SU 6497</t>
+          <t>SU 6481</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>SU 6515</t>
+          <t>SU 6497</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>SU 6519</t>
+          <t>SU 6515</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>SU 6093</t>
+          <t>SU 6519</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>SU 6703</t>
+          <t>SU 6093</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>SU 6097</t>
+          <t>SU 6703</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>SU 1454</t>
+          <t>SU 6097</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>SU 1530</t>
+          <t>SU 1454</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>SU 1524</t>
+          <t>SU 1530</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>00:46</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>SU 6299</t>
+          <t>SU 1524</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>SU 6061</t>
+          <t>SU 6299</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>SU 6</t>
+          <t>SU 6061</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>SU 1268</t>
+          <t>SU 6</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>SU 1044</t>
+          <t>SU 1268</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>SU 6213</t>
+          <t>SU 1044</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>SU 6313</t>
+          <t>SU 6213</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>SU 6059</t>
+          <t>SU 6313</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>SU 6243</t>
+          <t>SU 6059</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>SU 6271</t>
+          <t>SU 6243</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>SU 6089</t>
+          <t>SU 6271</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>SU 6579</t>
+          <t>SU 6089</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>N4* 59</t>
+          <t>SU 6579</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>SU 1260</t>
+          <t>N4* 59</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>SU 6707</t>
+          <t>SU 1260</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>SU 1458</t>
+          <t>SU 6707</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>22:39</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>SU 1072</t>
+          <t>SU 1458</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>22:39</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>SU 1110</t>
+          <t>SU 1072</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>SU 1000</t>
+          <t>SU 1110</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>SU 6153</t>
+          <t>SU 1000</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>SU 1460</t>
+          <t>SU 6153</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>SU 6057</t>
+          <t>SU 1460</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>SU 6197</t>
+          <t>SU 6057</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>SU 1028</t>
+          <t>SU 6197</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>SU 1468</t>
+          <t>SU 1028</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>SU 6361</t>
+          <t>SU 1468</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>SU 6661</t>
+          <t>SU 6361</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>SU 1440</t>
+          <t>SU 6661</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>SU 1326</t>
+          <t>SU 1440</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>SU 6079</t>
+          <t>SU 1326</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>SU 6289</t>
+          <t>SU 6079</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>SU 1586</t>
+          <t>SU 6289</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>SU 1510</t>
+          <t>SU 1586</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>SU 1464</t>
+          <t>SU 1510</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>SU 6365</t>
+          <t>SU 1464</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>23:38</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>SU 1382</t>
+          <t>SU 6365</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:38</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>SU 1410</t>
+          <t>SU 1382</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>SU 1416</t>
+          <t>SU 1410</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>SU 1234</t>
+          <t>SU 1416</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>SU 6253</t>
+          <t>SU 1234</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>SU 1744</t>
+          <t>SU 6253</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>SU 1734</t>
+          <t>SU 1744</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>SU 6235</t>
+          <t>SU 1734</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>SU 1442</t>
+          <t>SU 6235</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>SU 6287</t>
+          <t>SU 1442</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>SU 1750</t>
+          <t>SU 6287</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>SU 1004</t>
+          <t>SU 1750</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>SU 1176</t>
+          <t>SU 1004</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>SU 1124</t>
+          <t>SU 1176</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>SU 1246</t>
+          <t>SU 1124</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>SU 1130</t>
+          <t>SU 1246</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>SU 1548</t>
+          <t>SU 1130</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>SU 1016</t>
+          <t>SU 1548</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>YC 190</t>
+          <t>SU 1016</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>SU 1082</t>
+          <t>YC 190</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>SU 1226</t>
+          <t>SU 1082</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>SU 1140</t>
+          <t>SU 1226</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>SU 1422</t>
+          <t>SU 1140</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>SU 1006</t>
+          <t>SU 1422</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>SU 1322</t>
+          <t>SU 1006</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>SU 6809</t>
+          <t>SU 1322</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>SU 1484</t>
+          <t>SU 6809</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>SU 1400</t>
+          <t>SU 1484</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>SU 1060</t>
+          <t>SU 1400</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>SU 1010</t>
+          <t>SU 1060</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>SU 1128</t>
+          <t>SU 1010</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>SU 1762</t>
+          <t>SU 1128</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>22:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>SU 1466</t>
+          <t>SU 1762</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>02:35</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>SU 1504</t>
+          <t>SU 1466</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>02:35</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>SU 1310</t>
+          <t>SU 1504</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>SU 1214</t>
+          <t>SU 1310</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>SU 1418</t>
+          <t>SU 1214</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>SU 1198</t>
+          <t>SU 1418</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>SU 1512</t>
+          <t>SU 1198</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>SU 1534</t>
+          <t>SU 1512</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>SU 1538</t>
+          <t>SU 1534</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>SU 1700</t>
+          <t>SU 1538</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>SU 1704</t>
+          <t>SU 1700</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>SU 1450</t>
+          <t>SU 1704</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>SU 1318</t>
+          <t>SU 1450</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>SU 10</t>
+          <t>SU 1318</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>SU 6535</t>
+          <t>SU 10</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>SU 1394</t>
+          <t>SU 6535</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>SU 1562</t>
+          <t>SU 1394</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>01:39</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>SU 1232</t>
+          <t>SU 1562</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>01:39</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>SU 6241</t>
+          <t>SU 1232</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>SU 1638</t>
+          <t>SU 6241</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>SU 1148</t>
+          <t>SU 1638</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>00:33</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>SU 1056</t>
+          <t>SU 1148</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>SU 1714</t>
+          <t>SU 1056</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>SU 1726</t>
+          <t>SU 1714</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>03:35</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>SU 1132</t>
+          <t>SU 1726</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>03:35</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>SU 5802</t>
+          <t>SU 1132</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>SU 1262</t>
+          <t>SU 5802</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>SU 1136</t>
+          <t>SU 1262</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>SU 1122</t>
+          <t>SU 1136</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>SU 1404</t>
+          <t>SU 1122</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>SU 1052</t>
+          <t>SU 1404</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>SU 1002</t>
+          <t>SU 1052</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>SU 1212</t>
+          <t>SU 1002</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>SU 1118</t>
+          <t>SU 1212</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>SU 1018</t>
+          <t>SU 1118</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>SU 1680</t>
+          <t>SU 1018</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>SU 1606</t>
+          <t>SU 1680</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>SU 1008</t>
+          <t>SU 1606</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>SU 1646</t>
+          <t>SU 1008</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>SU 1424</t>
+          <t>SU 1646</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>SU 1054</t>
+          <t>SU 1424</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>02:21</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>SU 1516</t>
+          <t>SU 1054</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>02:21</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>SU 1348</t>
+          <t>SU 1516</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>SU 1192</t>
+          <t>SU 1348</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>SU 1314</t>
+          <t>SU 1192</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>SU 1432</t>
+          <t>SU 1314</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>SU 1688</t>
+          <t>SU 1432</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>SU 1532</t>
+          <t>SU 1688</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>SU 1194</t>
+          <t>SU 1532</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>SU 1420</t>
+          <t>SU 1194</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>SU 1306</t>
+          <t>SU 1420</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>01:17</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>SU 1242</t>
+          <t>SU 1306</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>01:17</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>SU 6385</t>
+          <t>SU 1242</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>SU 1312</t>
+          <t>SU 6385</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>SU 24</t>
+          <t>SU 1312</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>SU 1334</t>
+          <t>SU 24</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>SU 1428</t>
+          <t>SU 1334</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>00:37</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>SU 1304</t>
+          <t>SU 1428</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>00:37</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>SU 1486</t>
+          <t>SU 1304</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>SU 1258</t>
+          <t>SU 1486</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>SU 5822</t>
+          <t>SU 1258</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>SU 6255</t>
+          <t>SU 5822</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>23:11</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>SU 1244</t>
+          <t>SU 6255</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>23:11</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>SU 1014</t>
+          <t>SU 1244</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>SU 1544</t>
+          <t>SU 1014</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>SU 1490</t>
+          <t>SU 1544</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>SU 1024</t>
+          <t>SU 1490</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>DP* 6561</t>
+          <t>SU 1024</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>00:24</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>DP* 6567</t>
+          <t>DP* 6561</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>01:13</t>
+          <t>00:24</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -9192,12 +9192,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>DP* 6923</t>
+          <t>DP* 6567</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>01:13</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>DP* 6965</t>
+          <t>DP* 6923</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>DP* 6939</t>
+          <t>DP* 6965</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>DP* 6927</t>
+          <t>DP* 6939</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>DP* 6919</t>
+          <t>DP* 6927</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>DP* 6943</t>
+          <t>DP* 6919</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>DP* 6991</t>
+          <t>DP* 6943</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>DP* 6861</t>
+          <t>DP* 6991</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>DP* 6969</t>
+          <t>DP* 6861</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>DP* 6845</t>
+          <t>DP* 6969</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>DP* 6941</t>
+          <t>DP* 6845</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>DP* 5861</t>
+          <t>DP* 6941</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>DP* 6859</t>
+          <t>DP* 5861</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>DP* 6815</t>
+          <t>DP* 6859</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>DP* 6521</t>
+          <t>DP* 6815</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>DP* 6511</t>
+          <t>DP* 6521</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>DP* 6961</t>
+          <t>DP* 6511</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>DP* 6921</t>
+          <t>DP* 6961</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>DP* 6913</t>
+          <t>DP* 6921</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>DP* 6833</t>
+          <t>DP* 6913</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>DP* 6855</t>
+          <t>DP* 6833</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>DP* 6547</t>
+          <t>DP* 6855</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>DP* 6569</t>
+          <t>DP* 6547</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>DP* 6807</t>
+          <t>DP* 6569</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>DP* 6543</t>
+          <t>DP* 6807</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>23:46</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>DP* 6501</t>
+          <t>DP* 6543</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>DP* 6525</t>
+          <t>DP* 6501</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>00:11</t>
+          <t>00:35</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>DP* 6513</t>
+          <t>DP* 6525</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>01:28</t>
+          <t>00:11</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>DP* 6863</t>
+          <t>DP* 6513</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>01:28</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>DP* 6911</t>
+          <t>DP* 6863</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>DP* 6905</t>
+          <t>DP* 6911</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>DP* 6823</t>
+          <t>DP* 6905</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>DP* 6821</t>
+          <t>DP* 6823</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -10248,12 +10248,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>DP* 6915</t>
+          <t>DP* 6821</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -10280,12 +10280,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>DP* 6843</t>
+          <t>DP* 6915</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>DP* 6841</t>
+          <t>DP* 6843</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>DP* 6817</t>
+          <t>DP* 6841</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>DP* 6835</t>
+          <t>DP* 6817</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>DP* 6903</t>
+          <t>DP* 6835</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>DP* 6909</t>
+          <t>DP* 6903</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>DP* 6583</t>
+          <t>DP* 6909</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>DP* 6925</t>
+          <t>DP* 6583</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>DP* 6967</t>
+          <t>DP* 6925</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>DP* 6963</t>
+          <t>DP* 6967</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>DP* 6531</t>
+          <t>DP* 6963</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>DP* 6825</t>
+          <t>DP* 6531</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -10664,22 +10664,22 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>DP* 6831</t>
+          <t>DP* 6825</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>Kaliningrad</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
@@ -10718,7 +10718,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Kaliningrad</t>
         </is>
       </c>
     </row>
@@ -10760,12 +10760,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>JU 135</t>
+          <t>DP* 6831</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>SU 1966</t>
+          <t>JU 135</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>01:09</t>
+          <t>00:18</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>SU 426</t>
+          <t>SU 1966</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>01:09</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -10856,12 +10856,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>GA 9131</t>
+          <t>SU 426</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>CA 754</t>
+          <t>GA 9131</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>MU 6020</t>
+          <t>CA 754</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>GA 9033</t>
+          <t>MU 6020</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>SU 224</t>
+          <t>GA 9033</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>CZ 342</t>
+          <t>SU 224</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>SU 2124</t>
+          <t>CZ 342</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>SU 1936</t>
+          <t>SU 2124</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>01:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>SU 2136</t>
+          <t>SU 1936</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>01:59</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -11144,12 +11144,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>JU 131</t>
+          <t>SU 2136</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>SU 1842</t>
+          <t>JU 131</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>MU 2076</t>
+          <t>SU 1842</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>SU 294</t>
+          <t>MU 2076</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>SU 320</t>
+          <t>SU 294</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>SU 422</t>
+          <t>SU 320</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>N4* 1293</t>
+          <t>SU 422</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>SU 1862</t>
+          <t>N4* 1293</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>SU 2134</t>
+          <t>SU 1862</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>SU 1868</t>
+          <t>SU 2134</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>SU 1844</t>
+          <t>SU 1868</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>SU 420</t>
+          <t>SU 1844</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>SU 1870</t>
+          <t>SU 420</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>SU 232</t>
+          <t>SU 1870</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>SU 1942</t>
+          <t>SU 232</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>SU 1854</t>
+          <t>SU 1942</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>SU 220</t>
+          <t>SU 1854</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>SU 1882</t>
+          <t>SU 220</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>SU 1974</t>
+          <t>SU 1882</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>SU 296</t>
+          <t>SU 1974</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>SU 208</t>
+          <t>SU 296</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>SU 1946</t>
+          <t>SU 208</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -11848,12 +11848,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>GS 7942</t>
+          <t>SU 1946</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>HU 8298</t>
+          <t>GS 7942</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>3U 3888</t>
+          <t>HU 8298</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>STW 174</t>
+          <t>3U 3888</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>JU 137</t>
+          <t>STW 174</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>SU 1860</t>
+          <t>JU 137</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>SU 2160</t>
+          <t>SU 1860</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>B2 992</t>
+          <t>SU 2160</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>22:24</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>SU 424</t>
+          <t>B2 992</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>01:48</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -12136,12 +12136,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>SU 1836</t>
+          <t>SU 424</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>01:48</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>MU 592</t>
+          <t>SU 1836</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -12200,12 +12200,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>SU 204</t>
+          <t>MU 592</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -12232,12 +12232,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>FG 708</t>
+          <t>SU 204</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>02:19</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>SU 430</t>
+          <t>FG 708</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>02:19</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>SU 1856</t>
+          <t>SU 430</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -12328,12 +12328,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>UL 3034</t>
+          <t>SU 1856</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -12360,12 +12360,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>CZ 8004</t>
+          <t>UL 3034</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>SU 1872</t>
+          <t>CZ 8004</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>SU 1886</t>
+          <t>SU 1872</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -12456,12 +12456,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>SU 2144</t>
+          <t>SU 1886</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -12488,12 +12488,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>SU 1956</t>
+          <t>SU 2144</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>23:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -12520,12 +12520,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>SU 2148</t>
+          <t>SU 1956</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>02:36</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -12552,12 +12552,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>AT 221</t>
+          <t>SU 2148</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>02:36</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -12584,12 +12584,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>SU 2146</t>
+          <t>AT 221</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>B2 988</t>
+          <t>SU 2146</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>SU 5955</t>
+          <t>B2 988</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>SU 1832</t>
+          <t>SU 5955</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>SU 2126</t>
+          <t>SU 1832</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>SU 1864</t>
+          <t>SU 2126</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -12776,12 +12776,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>JU 133</t>
+          <t>SU 1864</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>SU 1850</t>
+          <t>JU 133</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>MFX 404</t>
+          <t>SU 1850</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>23:38</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>SU 298</t>
+          <t>MFX 404</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:38</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>SU 1834</t>
+          <t>SU 298</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>00:29</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>SU 2120</t>
+          <t>SU 1834</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>00:29</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>SU 2130</t>
+          <t>SU 2120</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -13000,12 +13000,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>STW 2</t>
+          <t>SU 2130</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>MU 248</t>
+          <t>STW 2</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>HU 7986</t>
+          <t>MU 248</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>SU 2172</t>
+          <t>HU 7986</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>SU 1830</t>
+          <t>SU 2172</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>SU 1954</t>
+          <t>SU 1830</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -13192,12 +13192,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>B2 976</t>
+          <t>SU 1954</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>STW 84</t>
+          <t>B2 976</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -13256,12 +13256,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>SU 1994</t>
+          <t>STW 84</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>SU 2142</t>
+          <t>SU 1994</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>SU 2122</t>
+          <t>SU 2142</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -13352,12 +13352,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>CZ 8028</t>
+          <t>SU 2122</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -13384,12 +13384,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>SU 284</t>
+          <t>CZ 8028</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -13416,12 +13416,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>SU 2138</t>
+          <t>SU 284</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>23:47</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>SU 2132</t>
+          <t>SU 2138</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>23:47</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>B2 978</t>
+          <t>SU 2132</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -13507,17 +13507,17 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>VKO</t>
+          <t>SVO</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>UT 333</t>
+          <t>B2 978</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -13544,12 +13544,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>UT 455</t>
+          <t>UT 333</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>UT 179</t>
+          <t>UT 455</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>DP* 113</t>
+          <t>UT 179</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>UT 295</t>
+          <t>DP* 113</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>UT 375</t>
+          <t>UT 295</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -13704,12 +13704,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>R3 687</t>
+          <t>UT 375</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -13736,12 +13736,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>UT 363</t>
+          <t>R3 687</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>01:52</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>UT 463</t>
+          <t>UT 363</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>01:52</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>6R* 544</t>
+          <t>UT 463</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>A4* 7035</t>
+          <t>6R* 544</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>DP* 209</t>
+          <t>A4* 7035</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -13896,12 +13896,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>UT 249</t>
+          <t>DP* 209</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -13928,12 +13928,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>DP* 423</t>
+          <t>UT 249</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -13960,12 +13960,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>R3 479</t>
+          <t>DP* 423</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -13992,12 +13992,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>UT 247</t>
+          <t>R3 479</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -14024,12 +14024,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>DP* 465</t>
+          <t>UT 247</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -14056,12 +14056,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>UT 267</t>
+          <t>DP* 465</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -14088,12 +14088,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>UT 397</t>
+          <t>UT 267</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -14120,12 +14120,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>UT 373</t>
+          <t>UT 397</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>SU 6162</t>
+          <t>UT 373</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>SU 6052</t>
+          <t>SU 6162</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -14216,12 +14216,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>SU 6006</t>
+          <t>SU 6052</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
@@ -14248,12 +14248,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>SU 6010</t>
+          <t>SU 6006</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>SU 6038</t>
+          <t>SU 6010</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
@@ -14312,12 +14312,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>SU 6178</t>
+          <t>SU 6038</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -14344,12 +14344,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>SU 6182</t>
+          <t>SU 6178</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>SU 6186</t>
+          <t>SU 6182</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>23:39</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -14408,12 +14408,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>SU 6190</t>
+          <t>SU 6186</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>23:39</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
@@ -14440,12 +14440,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>SU 6020</t>
+          <t>SU 6190</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>SU 6004</t>
+          <t>SU 6020</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -14504,12 +14504,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>SU 6008</t>
+          <t>SU 6004</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>SU 6026</t>
+          <t>SU 6008</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>SU 6176</t>
+          <t>SU 6026</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>R3 480</t>
+          <t>SU 6176</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -14632,12 +14632,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>SU 6180</t>
+          <t>R3 480</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>SU 6184</t>
+          <t>SU 6180</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -14686,7 +14686,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -14696,22 +14696,22 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>UT 573</t>
+          <t>SU 6184</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>Mineralnye Vody</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -14728,12 +14728,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>DP* 267</t>
+          <t>UT 573</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>Kaliningrad</t>
+          <t>Mineralnye Vody</t>
         </is>
       </c>
     </row>
@@ -14760,12 +14760,12 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>DP* 485</t>
+          <t>DP* 267</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -14775,14 +14775,14 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>Ulyanovsk</t>
+          <t>Kaliningrad</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -14802,19 +14802,19 @@
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Ulyanovsk</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -14824,29 +14824,29 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>DP* 205</t>
+          <t>DP* 485</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -14866,19 +14866,19 @@
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -14888,29 +14888,29 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>DP* 413</t>
+          <t>DP* 205</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -14930,19 +14930,19 @@
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -14952,29 +14952,29 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>DP* 435</t>
+          <t>DP* 413</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -14994,19 +14994,19 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Ufa</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -15016,22 +15016,22 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>DP* 407</t>
+          <t>DP* 435</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>00:09</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>Yekaterinburg</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
@@ -15070,7 +15070,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -15090,19 +15090,19 @@
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Yekaterinburg</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -15112,22 +15112,22 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>DP* 189</t>
+          <t>DP* 407</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>00:09</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -15186,19 +15186,19 @@
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Makhachkala</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -15208,22 +15208,22 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>DP* 115</t>
+          <t>DP* 189</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>Adler/Sochi</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -15262,7 +15262,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -15282,19 +15282,19 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Adler/Sochi</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -15304,22 +15304,22 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>DP* 421</t>
+          <t>DP* 115</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -15358,7 +15358,7 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -15378,19 +15378,19 @@
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Samara</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -15400,22 +15400,22 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>DP* 475</t>
+          <t>DP* 421</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>Saratov</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -15474,19 +15474,19 @@
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Saratov</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -15496,29 +15496,29 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>A4* 7007</t>
+          <t>DP* 475</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>multiple numeric gates</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>17, 7</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>multiple numeric gates</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>17, 7</t>
         </is>
       </c>
     </row>
@@ -15560,12 +15560,12 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>S7 4139</t>
+          <t>A4* 7007</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>01:41</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>NE* 619</t>
+          <t>S7 4139</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>03:27</t>
+          <t>01:41</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>UT 743</t>
+          <t>NE* 619</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>05:54</t>
+          <t>03:27</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -15656,12 +15656,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>UT 801</t>
+          <t>UT 743</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -15688,12 +15688,12 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>DV 810</t>
+          <t>UT 801</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>A4* 7009</t>
+          <t>DV 810</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -15752,12 +15752,12 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>S7 4137</t>
+          <t>A4* 7009</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -15784,12 +15784,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>TK 3015</t>
+          <t>S7 4137</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>02:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>KTK 511</t>
+          <t>TK 3015</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>02:03</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
@@ -15848,12 +15848,12 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>DP* 859</t>
+          <t>KTK 511</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>UT 785</t>
+          <t>DP* 859</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>DV 814</t>
+          <t>UT 785</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>TK 410</t>
+          <t>DV 814</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
@@ -15976,12 +15976,12 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>FIE 324</t>
+          <t>TK 410</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>02:54</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -16008,12 +16008,12 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>UT 809</t>
+          <t>FIE 324</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>02:54</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -16040,12 +16040,12 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>DV 816</t>
+          <t>UT 809</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -16072,12 +16072,12 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>TK 3179</t>
+          <t>DV 816</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>02:04</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -16104,12 +16104,12 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>PC 387</t>
+          <t>TK 3179</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>03:52</t>
+          <t>02:04</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -16136,12 +16136,12 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>NE* 603</t>
+          <t>PC 387</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>03:52</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -16168,12 +16168,12 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>PC 1459</t>
+          <t>NE* 603</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -16200,12 +16200,12 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>UT 745</t>
+          <t>PC 1459</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -16232,12 +16232,12 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>TK 1232</t>
+          <t>UT 745</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>PC 1581</t>
+          <t>TK 1232</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -16296,12 +16296,12 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>TK 412</t>
+          <t>PC 1581</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>00:31</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -16328,12 +16328,12 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>AJA 276</t>
+          <t>TK 412</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>02:19</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -16360,12 +16360,12 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>TK 422</t>
+          <t>AJA 276</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>02:33</t>
+          <t>02:19</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>TK 408</t>
+          <t>TK 422</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>02:33</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -16424,12 +16424,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>A4* 7029</t>
+          <t>TK 408</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -16456,12 +16456,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>AJA 588</t>
+          <t>A4* 7029</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>TK 414</t>
+          <t>AJA 588</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
@@ -16520,12 +16520,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>PC 389</t>
+          <t>TK 414</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -16552,12 +16552,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>TK 416</t>
+          <t>PC 389</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>TK 218</t>
+          <t>TK 416</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>01:56</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -16616,12 +16616,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>TK 420</t>
+          <t>TK 218</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>06:23</t>
+          <t>01:56</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -16648,12 +16648,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>DP* 839</t>
+          <t>TK 420</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:23</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>UT 783</t>
+          <t>DP* 839</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -16712,12 +16712,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>DP* 993</t>
+          <t>UT 783</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -16744,12 +16744,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>KTK 3007</t>
+          <t>DP* 993</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>KTK 3009</t>
+          <t>KTK 3007</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -16808,12 +16808,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>S7 4269</t>
+          <t>KTK 3009</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -16840,12 +16840,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>NE* 641</t>
+          <t>S7 4269</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -16872,12 +16872,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>TK 3061</t>
+          <t>NE* 641</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>01:32</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -16904,12 +16904,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>AJA 278</t>
+          <t>TK 3061</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>01:32</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>DP* 835</t>
+          <t>AJA 278</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>S7 4321</t>
+          <t>DP* 835</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -17000,12 +17000,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>TK 3013</t>
+          <t>S7 4321</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -17032,12 +17032,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>UT 805</t>
+          <t>TK 3013</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -17064,12 +17064,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>S7 4317</t>
+          <t>UT 805</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -17096,12 +17096,12 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>NE* 611</t>
+          <t>S7 4317</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>TK 3003</t>
+          <t>NE* 611</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>S7 4327</t>
+          <t>TK 3003</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
@@ -17192,12 +17192,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>DP* 855</t>
+          <t>S7 4327</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -17224,12 +17224,12 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>SHS 510</t>
+          <t>DP* 855</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>S7 4311</t>
+          <t>SHS 510</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -17288,12 +17288,12 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>S7 4265</t>
+          <t>S7 4311</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
@@ -17320,12 +17320,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>PC 1522</t>
+          <t>S7 4265</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>01:59</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -17352,12 +17352,12 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>NE* 605</t>
+          <t>PC 1522</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>06:16</t>
+          <t>01:59</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
@@ -17384,12 +17384,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>S7 4381</t>
+          <t>NE* 605</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>EK 2311</t>
+          <t>S7 4381</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
@@ -17448,12 +17448,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>S7 4319</t>
+          <t>EK 2311</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -17480,12 +17480,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>TK 3037</t>
+          <t>S7 4319</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>02:17</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
@@ -17512,12 +17512,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>PC 1457</t>
+          <t>TK 3037</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>02:17</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>PC 1577</t>
+          <t>PC 1457</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>01:32</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
@@ -17576,12 +17576,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>EK 2323</t>
+          <t>PC 1577</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>03:20</t>
+          <t>01:32</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -17608,12 +17608,12 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>PC 391</t>
+          <t>EK 2323</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>03:20</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
@@ -17640,12 +17640,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>B2 982</t>
+          <t>PC 391</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -17672,12 +17672,12 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>B2 980</t>
+          <t>B2 982</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
@@ -17704,12 +17704,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>TK 212</t>
+          <t>B2 980</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>01:16</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -17736,12 +17736,12 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>A9 931</t>
+          <t>TK 212</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>05:25</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
@@ -17768,12 +17768,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>A4* 7053</t>
+          <t>A9 931</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>A9 925</t>
+          <t>A4* 7053</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
@@ -17822,7 +17822,7 @@
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
@@ -17832,29 +17832,29 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>KTK 3013</t>
+          <t>A9 925</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
@@ -17874,19 +17874,19 @@
       </c>
       <c r="E545" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Antalya</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
@@ -17896,22 +17896,22 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>HYY 134</t>
+          <t>KTK 3013</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>01:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F547" s="2" t="inlineStr">
@@ -17960,22 +17960,22 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>DP* 733</t>
+          <t>HYY 134</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>01:39</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>Termez</t>
+          <t>Yerevan</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="E549" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F549" s="2" t="inlineStr">
@@ -18014,7 +18014,7 @@
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
@@ -18034,19 +18034,19 @@
       </c>
       <c r="E550" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Termez</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -18056,22 +18056,22 @@
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>DP* 995</t>
+          <t>DP* 733</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>01:39</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="E552" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F552" s="2" t="inlineStr">
@@ -18110,7 +18110,7 @@
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
@@ -18130,19 +18130,19 @@
       </c>
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Istanbul</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
@@ -18152,22 +18152,22 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>DP* 711</t>
+          <t>DP* 995</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>Samarkand</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
@@ -18206,7 +18206,7 @@
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
@@ -18226,19 +18226,19 @@
       </c>
       <c r="E556" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Samarkand</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
@@ -18248,22 +18248,22 @@
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>DP* 997</t>
+          <t>DP* 711</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>Samarkand</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -18322,19 +18322,19 @@
       </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Samarkand</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -18344,22 +18344,22 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>DP* 741</t>
+          <t>DP* 997</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>Tashkent</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="E561" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F561" s="2" t="inlineStr">
@@ -18398,7 +18398,7 @@
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -18418,19 +18418,19 @@
       </c>
       <c r="E562" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Tashkent</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -18440,22 +18440,22 @@
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>DP* 743</t>
+          <t>DP* 741</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F563" s="2" t="inlineStr">
         <is>
-          <t>Osh</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="E564" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F564" s="2" t="inlineStr">
@@ -18494,7 +18494,7 @@
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -18514,19 +18514,19 @@
       </c>
       <c r="E565" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F565" s="2" t="inlineStr">
         <is>
-          <t>Actual departure time exists, but status text was parsed as Total.</t>
+          <t>Osh</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -18536,22 +18536,22 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>DP* 713</t>
+          <t>DP* 743</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
-          <t>missing gate</t>
+          <t>weak status text from source</t>
         </is>
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
-          <t>Samarkand</t>
+          <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="E567" s="2" t="inlineStr">
         <is>
-          <t>missing terminal</t>
+          <t>missing gate</t>
         </is>
       </c>
       <c r="F567" s="2" t="inlineStr">
@@ -18590,7 +18590,7 @@
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -18610,17 +18610,49 @@
       </c>
       <c r="E568" s="2" t="inlineStr">
         <is>
-          <t>weak status text from source</t>
+          <t>missing terminal</t>
         </is>
       </c>
       <c r="F568" s="2" t="inlineStr">
         <is>
+          <t>Samarkand</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>VKO</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>DP* 713</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>weak status text from source</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
           <t>Actual departure time exists, but status text was parsed as Total.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F568"/>
+  <autoFilter ref="A1:F569"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18669,7 +18701,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4">
@@ -18689,7 +18721,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6">
